--- a/data/video_scenario.xlsx
+++ b/data/video_scenario.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\veo3\project\lion\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59E3329E-56B7-440D-9A53-5736CDC6E0EB}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{888DFB82-9938-411A-B2AD-A807568E530E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="22">
   <si>
     <t>template_key</t>
   </si>
@@ -32,30 +32,6 @@
     <t>note</t>
   </si>
   <si>
-    <t>Mẫu_Ảnh_Ngang_Anime</t>
-  </si>
-  <si>
-    <t>Anime style illustration of {0} wearing {1.0}, trending on pixiv, highly detailed --ar 16:9</t>
-  </si>
-  <si>
-    <t>Chỉ dùng {0} và {1}, bỏ qua ảnh tham chiếu</t>
-  </si>
-  <si>
-    <t>Mẫu_Ảnh_Ngang_Cinematic</t>
-  </si>
-  <si>
-    <t>"A cinematic scene of {1.0} fighting against {1.1} inside {2.0}, action: {0}"</t>
-  </si>
-  <si>
-    <t>Dùng đầy đủ cả 3 tham số đầu vào</t>
-  </si>
-  <si>
-    <t>NhanVat_and_Action</t>
-  </si>
-  <si>
-    <t>"{1.0}   {0}"</t>
-  </si>
-  <si>
     <t>scene_id</t>
   </si>
   <si>
@@ -80,26 +56,130 @@
     <t>file_name</t>
   </si>
   <si>
-    <t>scena_1</t>
-  </si>
-  <si>
-    <t>reading book</t>
-  </si>
-  <si>
-    <t>scena_2</t>
-  </si>
-  <si>
-    <t>close eyes</t>
-  </si>
-  <si>
-    <t>nvLion</t>
+    <t>vid_1</t>
+  </si>
+  <si>
+    <t>vid_2</t>
+  </si>
+  <si>
+    <t>vid_3</t>
+  </si>
+  <si>
+    <t>vid_4</t>
+  </si>
+  <si>
+    <t>vid_5</t>
+  </si>
+  <si>
+    <t>Normal</t>
+  </si>
+  <si>
+    <t>video_Anh_6x_4s</t>
+  </si>
+  <si>
+    <t>img_100</t>
+  </si>
+  <si>
+    <t>img_101</t>
+  </si>
+  <si>
+    <t>img_102</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Create a continuous 5-second video that </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>pans and transitions sequentially through the 6-panel storyboard</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> layout of the selected image. The camera must start with a full-frame shot focusing exactly on Panel 1 (top-left). Then, the camera must </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>smoothly glide, pan, and transform forward through Panel 2, Panel 3, Panel 4, and Panel 5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> in strict chronological order, creating a seamless frame-by-frame narrative flow. Finally, the video must </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>settle and resolve perfectly</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">on the content of Panel 6 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(bottom-right) as the cinematic ending. Ensure hyper-realistic wildlife documentary motion, smooth camera tracking, photorealistic textures, and zero abrupt cuts between the panels.</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -111,6 +191,15 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -148,10 +237,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -455,7 +547,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.85546875" bestFit="1" customWidth="1"/>
@@ -466,68 +558,89 @@
     <col min="6" max="6" width="36.42578125" customWidth="1"/>
     <col min="7" max="7" width="33.7109375" customWidth="1"/>
     <col min="8" max="8" width="25.28515625" customWidth="1"/>
-    <col min="9" max="9" width="22.5703125" customWidth="1"/>
+    <col min="9" max="9" width="38.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D2" t="s">
-        <v>23</v>
+        <v>17</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>19</v>
       </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="E7" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -536,7 +649,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="36" customWidth="1"/>
@@ -554,37 +667,21 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="119.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" t="s">
-        <v>5</v>
+        <v>17</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/data/video_scenario.xlsx
+++ b/data/video_scenario.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\veo3\project\lion\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{888DFB82-9938-411A-B2AD-A807568E530E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F29653D9-D896-4B98-8C8A-D0D37C4812FB}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="25">
   <si>
     <t>template_key</t>
   </si>
@@ -65,29 +65,23 @@
     <t>vid_3</t>
   </si>
   <si>
-    <t>vid_4</t>
-  </si>
-  <si>
-    <t>vid_5</t>
-  </si>
-  <si>
     <t>Normal</t>
   </si>
   <si>
     <t>video_Anh_6x_4s</t>
   </si>
   <si>
-    <t>img_100</t>
-  </si>
-  <si>
-    <t>img_101</t>
-  </si>
-  <si>
-    <t>img_102</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Create a continuous 5-second video that </t>
+    <t>On the open grasslands, everything appears calm.</t>
+  </si>
+  <si>
+    <t>A small herd of antelope grazes peacefully.</t>
+  </si>
+  <si>
+    <t>A close-up shot focused on thick</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Create a continuous -second video that </t>
     </r>
     <r>
       <rPr>
@@ -173,6 +167,21 @@
       </rPr>
       <t>(bottom-right) as the cinematic ending. Ensure hyper-realistic wildlife documentary motion, smooth camera tracking, photorealistic textures, and zero abrupt cuts between the panels.</t>
     </r>
+  </si>
+  <si>
+    <t>Create a seamless, continuous 4-second video that morphs and transitions smoothly between the two selected images, starting with the first image and ending perfectly on the second image. The text "{0}" must be clearly printed as a static, clean, white minimalist subtitle at the bottom center of the screen throughout the entire video to distinguish this scene. Through highly fluid animation, the elements must transform continuously forward without any cuts. Ensure hyper-realistic textures, consistent cinematic wildlife style, and extremely smooth motion interpolation, while keeping the text label completely rigid and crisp.</t>
+  </si>
+  <si>
+    <t>Only_title_4s</t>
+  </si>
+  <si>
+    <t>mage_1, mage_2</t>
+  </si>
+  <si>
+    <t>mage_2, mage_3</t>
+  </si>
+  <si>
+    <t>mage_3, mage_4</t>
   </si>
 </sst>
 </file>
@@ -590,26 +599,32 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>17</v>
+        <v>21</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>16</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>12</v>
       </c>
       <c r="B3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
@@ -617,26 +632,13 @@
         <v>13</v>
       </c>
       <c r="B4" t="s">
-        <v>17</v>
+        <v>21</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>18</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>15</v>
-      </c>
-      <c r="B6" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
@@ -649,7 +651,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="36" customWidth="1"/>
@@ -669,15 +671,23 @@
     </row>
     <row r="2" spans="1:3" ht="119.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>16</v>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" t="s">
+        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/data/video_scenario.xlsx
+++ b/data/video_scenario.xlsx
@@ -8,180 +8,159 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\veo3\project\lion\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F29653D9-D896-4B98-8C8A-D0D37C4812FB}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0ED8B05-EF18-4BBF-9438-F707E36B98D1}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Script" sheetId="4" r:id="rId1"/>
-    <sheet name="Templates" sheetId="1" r:id="rId2"/>
+    <sheet name="Script" sheetId="1" r:id="rId1"/>
+    <sheet name="Templates" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="44">
+  <si>
+    <t>scene_id</t>
+  </si>
   <si>
     <t>template_key</t>
   </si>
   <si>
+    <t>prompt_core</t>
+  </si>
+  <si>
+    <t>character_list</t>
+  </si>
+  <si>
+    <t>reference_list</t>
+  </si>
+  <si>
+    <t>final_prompt</t>
+  </si>
+  <si>
+    <t>status_time</t>
+  </si>
+  <si>
+    <t>output_id</t>
+  </si>
+  <si>
+    <t>file_name</t>
+  </si>
+  <si>
+    <t>Normal</t>
+  </si>
+  <si>
     <t>template_value</t>
   </si>
   <si>
     <t>note</t>
   </si>
   <si>
-    <t>scene_id</t>
-  </si>
-  <si>
-    <t>prompt_core</t>
-  </si>
-  <si>
-    <t>character_list</t>
-  </si>
-  <si>
-    <t>reference_list</t>
-  </si>
-  <si>
-    <t>final_prompt</t>
-  </si>
-  <si>
-    <t>status_time</t>
-  </si>
-  <si>
-    <t>output_id</t>
-  </si>
-  <si>
-    <t>file_name</t>
-  </si>
-  <si>
-    <t>vid_1</t>
-  </si>
-  <si>
-    <t>vid_2</t>
-  </si>
-  <si>
-    <t>vid_3</t>
-  </si>
-  <si>
-    <t>Normal</t>
-  </si>
-  <si>
     <t>video_Anh_6x_4s</t>
   </si>
   <si>
-    <t>On the open grasslands, everything appears calm.</t>
-  </si>
-  <si>
-    <t>A small herd of antelope grazes peacefully.</t>
-  </si>
-  <si>
-    <t>A close-up shot focused on thick</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Create a continuous -second video that </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>pans and transitions sequentially through the 6-panel storyboard</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> layout of the selected image. The camera must start with a full-frame shot focusing exactly on Panel 1 (top-left). Then, the camera must </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>smoothly glide, pan, and transform forward through Panel 2, Panel 3, Panel 4, and Panel 5</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> in strict chronological order, creating a seamless frame-by-frame narrative flow. Finally, the video must </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>settle and resolve perfectly</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">on the content of Panel 6 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(bottom-right) as the cinematic ending. Ensure hyper-realistic wildlife documentary motion, smooth camera tracking, photorealistic textures, and zero abrupt cuts between the panels.</t>
-    </r>
+    <t>Create a continuous -second video that pans and transitions sequentially through the 6-panel storyboard layout of the selected image. The camera must start with a full-frame shot focusing exactly on Panel 1 (top-left). Then, the camera must smoothly glide, pan, and transform forward through Panel 2, Panel 3, Panel 4, and Panel 5 in strict chronological order, creating a seamless frame-by-frame narrative flow. Finally, the video must settle and resolve perfectly on the content of Panel 6 (bottom-right) as the cinematic ending. Ensure hyper-realistic wildlife documentary motion, smooth camera tracking, photorealistic textures, and zero abrupt cuts between the panels.</t>
+  </si>
+  <si>
+    <t>{0}</t>
+  </si>
+  <si>
+    <t>Only_title_4s</t>
   </si>
   <si>
     <t>Create a seamless, continuous 4-second video that morphs and transitions smoothly between the two selected images, starting with the first image and ending perfectly on the second image. The text "{0}" must be clearly printed as a static, clean, white minimalist subtitle at the bottom center of the screen throughout the entire video to distinguish this scene. Through highly fluid animation, the elements must transform continuously forward without any cuts. Ensure hyper-realistic textures, consistent cinematic wildlife style, and extremely smooth motion interpolation, while keeping the text label completely rigid and crisp.</t>
   </si>
   <si>
-    <t>Only_title_4s</t>
-  </si>
-  <si>
-    <t>mage_1, mage_2</t>
-  </si>
-  <si>
-    <t>mage_2, mage_3</t>
-  </si>
-  <si>
-    <t>mage_3, mage_4</t>
+    <t>Scene 1</t>
+  </si>
+  <si>
+    <t>Scene 2</t>
+  </si>
+  <si>
+    <t>Scene 3</t>
+  </si>
+  <si>
+    <t>Scene 4</t>
+  </si>
+  <si>
+    <t>Scene 5</t>
+  </si>
+  <si>
+    <t>Scene 6</t>
+  </si>
+  <si>
+    <t>Scene 7</t>
+  </si>
+  <si>
+    <t>Scene 8</t>
+  </si>
+  <si>
+    <t>C_Herd</t>
+  </si>
+  <si>
+    <t>key_10,key_11</t>
+  </si>
+  <si>
+    <t>key_11,key_12</t>
+  </si>
+  <si>
+    <t>key_12,key_13</t>
+  </si>
+  <si>
+    <t>key_13,key_14</t>
+  </si>
+  <si>
+    <t>key_14,key_15</t>
+  </si>
+  <si>
+    <t>key_15,key_16</t>
+  </si>
+  <si>
+    <t>key_16,key_17</t>
+  </si>
+  <si>
+    <t>key_17,key_18</t>
+  </si>
+  <si>
+    <t>C_Lioness</t>
+  </si>
+  <si>
+    <t>C_Lioness, C_Antelope</t>
+  </si>
+  <si>
+    <t>Locked Attributes: {1.0} (African antelopes, tan-brown fur, slender build).
+Motion Transition: Smooth continuous camera push-in from {2.0} wide shot to {2.1} close-up. Seamless interpolation showing they are grazing naturally with grass swaying gently in the wind, smoothly shifting focus as one of them twitches its ears. Fluid motion, photorealistic 4k.</t>
+  </si>
+  <si>
+    <t>Locked Attributes: {1.0} (sleek golden-tan female lion, amber eyes).
+Motion Transition: Fluid character motion transition. She moves smoothly from the static crouching position in {2.0} to taking a slow, stealthy, deliberate step forward into {2.1}. Low-angle tracking shot, soft natural wind moving through her golden fur and dry grass continuously.</t>
+  </si>
+  <si>
+    <t>Locked Attributes: {1.0} (muscular golden female lion) &amp; {1.1} (small juvenile antelope).
+Motion Transition: High-speed fluid sprint tracking. Seamless motion transition as she bursts from stillness in {2.0} into a full-speed chase, zeroing in on it as it lags behind in {2.1}. Continuous camera movement, dynamic muscle contraction, smooth dust trail.</t>
+  </si>
+  <si>
+    <t>Locked Attributes: {1.0}(golden female lion) &amp; {1.1} (young small juvenile antelope).
+Motion Transition: Hyper-smooth high-velocity turn sequence. It smoothly pivots from a straight sprint in {2.0} into a sharp zigzag evasion in {2.1}. She fluidly mirrors the turn immediately behind it, seamless tracking camera angle, natural dirt physics.</t>
+  </si>
+  <si>
+    <t>Locked Attributes: {1.0} (powerful female lion) &amp; {1.1} (small young antelope).
+Motion Transition: Dramatic airborne leap interpolation. She smoothly springs off the ground from {2.0}, launching into mid-air and landing with physical impact on its back in {2.1}. Seamless arc motion, slow-motion physics, fluid particle explosion of dust.</t>
+  </si>
+  <si>
+    <t>Locked Attributes: {1.0} (exhausted golden female lion) &amp; {1.1} (young antelope).
+Motion Transition: Slow continuous downward-to-forward motion transition. The intense impact in {2.0} smoothly settles into {2.1} as dust slowly dissipates. Her chest heaves naturally with heavy breathing before she slowly stands up and begins dragging it forward across the grass.</t>
+  </si>
+  <si>
+    <t>Locked Attributes: {1.0} (adult female lion, sleek golden fur, muscular, amber eyes).
+Motion Transition: Seamless focus-rack transition. Smooth camera pan moving from the grazing antelope in {2.0} down to the golden grass, revealing C_Lioness crouching in {2.1}. Fluid animation of lioness shifting into a low tense posture, amber eyes tracking target smoothly.</t>
+  </si>
+  <si>
+    <t>Locked Attributes: {1.0} (African antelopes, alert behavior).
+Motion Transition: Fast dynamic transition from calm to panic. C_Herd in {2.0} abruptly snaps their heads up and accelerates into a full scatter toward {2.1}. Smooth motion interpolation of hooves kicking up dust clouds, realistic motion blur, fluid animal running animation.</t>
   </si>
 </sst>
 </file>
@@ -246,13 +225,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -555,16 +540,16 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:I7"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:I10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.140625" customWidth="1"/>
     <col min="2" max="2" width="20" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="36.28515625" customWidth="1"/>
-    <col min="4" max="4" width="18.85546875" customWidth="1"/>
+    <col min="3" max="3" width="122.85546875" customWidth="1"/>
+    <col min="4" max="4" width="60" customWidth="1"/>
     <col min="5" max="5" width="29.28515625" customWidth="1"/>
-    <col min="6" max="6" width="36.42578125" customWidth="1"/>
+    <col min="6" max="6" width="25.7109375" customWidth="1"/>
     <col min="7" max="7" width="33.7109375" customWidth="1"/>
     <col min="8" max="8" width="25.28515625" customWidth="1"/>
     <col min="9" max="9" width="38.42578125" customWidth="1"/>
@@ -572,77 +557,178 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2" t="s">
+    </row>
+    <row r="2" spans="1:9" ht="137.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+    </row>
+    <row r="3" spans="1:9" ht="125.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+    </row>
+    <row r="4" spans="1:9" ht="108" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F4" s="3"/>
+    </row>
+    <row r="5" spans="1:9" ht="87" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F5" s="3"/>
+    </row>
+    <row r="6" spans="1:9" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E2" s="2" t="s">
+      <c r="B6" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F6" s="3"/>
+    </row>
+    <row r="7" spans="1:9" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3" t="s">
-        <v>21</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E3" s="2" t="s">
+      <c r="B7" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E4" s="2" t="s">
+      <c r="B8" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="E7" s="2"/>
+      <c r="B9" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -650,7 +736,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -660,38 +746,41 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="119.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B4" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageSetup orientation="portrait"/>
 </worksheet>
 </file>